--- a/LHF Dam season 2026-2027.xlsx
+++ b/LHF Dam season 2026-2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AA11A1-481F-4B4D-8355-23C90AA8B993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01497651-9F9C-49D4-ADA5-9C31F5A92145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lulea HF - Box score" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="192">
   <si>
     <t>Shirt number</t>
   </si>
@@ -536,6 +536,69 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>22:34</t>
+  </si>
+  <si>
+    <t>22:04</t>
+  </si>
+  <si>
+    <t>19:23</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>39%</t>
+  </si>
+  <si>
+    <t>18:26</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>02:09</t>
+  </si>
+  <si>
+    <t>21:09</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:19</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
+    <t>03:01</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT34"/>
+  <dimension ref="A1:AT51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.81640625" style="7" customWidth="1"/>
@@ -5379,8 +5442,8 @@
       <c r="D32" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>79</v>
+      <c r="E32" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>158</v>
@@ -5783,6 +5846,2386 @@
         <v>1</v>
       </c>
       <c r="AT34" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="7">
+        <v>3</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" s="7">
+        <v>21</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N35" s="7">
+        <v>1</v>
+      </c>
+      <c r="O35" s="7">
+        <v>1</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>1</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S35" s="7">
+        <v>14</v>
+      </c>
+      <c r="T35" s="7">
+        <v>5</v>
+      </c>
+      <c r="U35" s="7">
+        <v>9</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="W35" s="7">
+        <v>2</v>
+      </c>
+      <c r="X35" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA35" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="AB35" s="7">
+        <v>-0.67</v>
+      </c>
+      <c r="AC35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD35" s="7">
+        <v>1.49</v>
+      </c>
+      <c r="AE35" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AF35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="7">
+        <v>-15</v>
+      </c>
+      <c r="AH35" s="7">
+        <v>15</v>
+      </c>
+      <c r="AI35" s="7">
+        <v>30</v>
+      </c>
+      <c r="AJ35" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK35" s="7">
+        <v>9</v>
+      </c>
+      <c r="AL35" s="7">
+        <v>21</v>
+      </c>
+      <c r="AM35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN35" s="7">
+        <v>17</v>
+      </c>
+      <c r="AO35" s="7">
+        <v>8</v>
+      </c>
+      <c r="AP35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ35" s="7">
+        <v>3</v>
+      </c>
+      <c r="AR35" s="7">
+        <v>3</v>
+      </c>
+      <c r="AS35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT35" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="7">
+        <v>20</v>
+      </c>
+      <c r="H36" s="7">
+        <v>1</v>
+      </c>
+      <c r="I36" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L36" s="7">
+        <v>1</v>
+      </c>
+      <c r="M36" s="7">
+        <v>2</v>
+      </c>
+      <c r="N36" s="7">
+        <v>2</v>
+      </c>
+      <c r="O36" s="7">
+        <v>2</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>2</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S36" s="7">
+        <v>6</v>
+      </c>
+      <c r="T36" s="7">
+        <v>4</v>
+      </c>
+      <c r="U36" s="7">
+        <v>2</v>
+      </c>
+      <c r="V36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="W36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X36" s="7">
+        <v>6</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA36" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="AB36" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="AC36" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="AD36" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="AE36" s="7">
+        <v>2</v>
+      </c>
+      <c r="AF36" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="AG36" s="7">
+        <v>-15</v>
+      </c>
+      <c r="AH36" s="7">
+        <v>15</v>
+      </c>
+      <c r="AI36" s="7">
+        <v>30</v>
+      </c>
+      <c r="AJ36" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK36" s="7">
+        <v>9</v>
+      </c>
+      <c r="AL36" s="7">
+        <v>20</v>
+      </c>
+      <c r="AM36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AN36" s="7">
+        <v>7</v>
+      </c>
+      <c r="AO36" s="7">
+        <v>2</v>
+      </c>
+      <c r="AP36" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ36" s="7">
+        <v>2</v>
+      </c>
+      <c r="AR36" s="7">
+        <v>1</v>
+      </c>
+      <c r="AS36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT36" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="7">
+        <v>3</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="7">
+        <v>21</v>
+      </c>
+      <c r="H37" s="7">
+        <v>1</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M37" s="7">
+        <v>1</v>
+      </c>
+      <c r="N37" s="7">
+        <v>1</v>
+      </c>
+      <c r="O37" s="7">
+        <v>1</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S37" s="7">
+        <v>1</v>
+      </c>
+      <c r="T37" s="7">
+        <v>1</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W37" s="7">
+        <v>1</v>
+      </c>
+      <c r="X37" s="7">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA37" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>-0.73</v>
+      </c>
+      <c r="AC37" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AD37" s="7">
+        <v>1.21</v>
+      </c>
+      <c r="AE37" s="7">
+        <v>1.94</v>
+      </c>
+      <c r="AF37" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="AG37" s="7">
+        <v>-16</v>
+      </c>
+      <c r="AH37" s="7">
+        <v>11</v>
+      </c>
+      <c r="AI37" s="7">
+        <v>27</v>
+      </c>
+      <c r="AJ37" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK37" s="7">
+        <v>7</v>
+      </c>
+      <c r="AL37" s="7">
+        <v>20</v>
+      </c>
+      <c r="AM37" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN37" s="7">
+        <v>6</v>
+      </c>
+      <c r="AO37" s="7">
+        <v>2</v>
+      </c>
+      <c r="AP37" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ37" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR37" s="7">
+        <v>5</v>
+      </c>
+      <c r="AS37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT37" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="7">
+        <v>3</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G38" s="7">
+        <v>25</v>
+      </c>
+      <c r="H38" s="7">
+        <v>1</v>
+      </c>
+      <c r="I38" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M38" s="7">
+        <v>1</v>
+      </c>
+      <c r="N38" s="7">
+        <v>2</v>
+      </c>
+      <c r="O38" s="7">
+        <v>2</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S38" s="7">
+        <v>2</v>
+      </c>
+      <c r="T38" s="7">
+        <v>2</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V38" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X38" s="7">
+        <v>4</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="AB38" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="AC38" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="AD38" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="AE38" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="AF38" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="AG38" s="7">
+        <v>5</v>
+      </c>
+      <c r="AH38" s="7">
+        <v>12</v>
+      </c>
+      <c r="AI38" s="7">
+        <v>7</v>
+      </c>
+      <c r="AJ38" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK38" s="7">
+        <v>9</v>
+      </c>
+      <c r="AL38" s="7">
+        <v>5</v>
+      </c>
+      <c r="AM38" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN38" s="7">
+        <v>7</v>
+      </c>
+      <c r="AO38" s="7">
+        <v>3</v>
+      </c>
+      <c r="AP38" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AQ38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR38" s="7">
+        <v>2</v>
+      </c>
+      <c r="AS38" s="7">
+        <v>2</v>
+      </c>
+      <c r="AT38" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="7">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" s="7">
+        <v>22</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="J39" s="7">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L39" s="7">
+        <v>1</v>
+      </c>
+      <c r="M39" s="7">
+        <v>1</v>
+      </c>
+      <c r="N39" s="7">
+        <v>1</v>
+      </c>
+      <c r="O39" s="7">
+        <v>2</v>
+      </c>
+      <c r="P39" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S39" s="7">
+        <v>6</v>
+      </c>
+      <c r="T39" s="7">
+        <v>3</v>
+      </c>
+      <c r="U39" s="7">
+        <v>3</v>
+      </c>
+      <c r="V39" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="W39" s="7">
+        <v>1</v>
+      </c>
+      <c r="X39" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z39" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="AC39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD39" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="AE39" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="AF39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="7">
+        <v>-5</v>
+      </c>
+      <c r="AH39" s="7">
+        <v>9</v>
+      </c>
+      <c r="AI39" s="7">
+        <v>14</v>
+      </c>
+      <c r="AJ39" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK39" s="7">
+        <v>6</v>
+      </c>
+      <c r="AL39" s="7">
+        <v>10</v>
+      </c>
+      <c r="AM39" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN39" s="7">
+        <v>14</v>
+      </c>
+      <c r="AO39" s="7">
+        <v>4</v>
+      </c>
+      <c r="AP39" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR39" s="7">
+        <v>3</v>
+      </c>
+      <c r="AS39" s="7">
+        <v>2</v>
+      </c>
+      <c r="AT39" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="7">
+        <v>3</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="7">
+        <v>23</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="7">
+        <v>1</v>
+      </c>
+      <c r="L40" s="7">
+        <v>1</v>
+      </c>
+      <c r="M40" s="7">
+        <v>1</v>
+      </c>
+      <c r="N40" s="7">
+        <v>0</v>
+      </c>
+      <c r="O40" s="7">
+        <v>1</v>
+      </c>
+      <c r="P40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W40" s="7">
+        <v>1</v>
+      </c>
+      <c r="X40" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>2</v>
+      </c>
+      <c r="Z40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>-0.66</v>
+      </c>
+      <c r="AC40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="AE40" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="AF40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="7">
+        <v>-7</v>
+      </c>
+      <c r="AH40" s="7">
+        <v>9</v>
+      </c>
+      <c r="AI40" s="7">
+        <v>16</v>
+      </c>
+      <c r="AJ40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK40" s="7">
+        <v>6</v>
+      </c>
+      <c r="AL40" s="7">
+        <v>12</v>
+      </c>
+      <c r="AM40" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN40" s="7">
+        <v>8</v>
+      </c>
+      <c r="AO40" s="7">
+        <v>5</v>
+      </c>
+      <c r="AP40" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS40" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT40" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="7">
+        <v>3</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="7">
+        <v>18</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41" s="7">
+        <v>-2</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P41" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X41" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="AB41" s="7">
+        <v>-0.89</v>
+      </c>
+      <c r="AC41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD41" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="AE41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="7">
+        <v>-13</v>
+      </c>
+      <c r="AH41" s="7">
+        <v>3</v>
+      </c>
+      <c r="AI41" s="7">
+        <v>16</v>
+      </c>
+      <c r="AJ41" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK41" s="7">
+        <v>2</v>
+      </c>
+      <c r="AL41" s="7">
+        <v>7</v>
+      </c>
+      <c r="AM41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN41" s="7">
+        <v>5</v>
+      </c>
+      <c r="AO41" s="7">
+        <v>2</v>
+      </c>
+      <c r="AP41" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR41" s="7">
+        <v>2</v>
+      </c>
+      <c r="AS41" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT41" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A42" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="7">
+        <v>3</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42" s="7">
+        <v>14</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N42" s="7">
+        <v>-1</v>
+      </c>
+      <c r="O42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="AC42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="AE42" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="AF42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG42" s="7">
+        <v>-7</v>
+      </c>
+      <c r="AH42" s="7">
+        <v>3</v>
+      </c>
+      <c r="AI42" s="7">
+        <v>10</v>
+      </c>
+      <c r="AJ42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AK42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="7">
+        <v>5</v>
+      </c>
+      <c r="AM42" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN42" s="7">
+        <v>3</v>
+      </c>
+      <c r="AO42" s="7">
+        <v>2</v>
+      </c>
+      <c r="AP42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR42" s="7">
+        <v>2</v>
+      </c>
+      <c r="AS42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT42" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A43" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="7">
+        <v>3</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G43" s="7">
+        <v>3</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE43" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="AF43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG43" s="7">
+        <v>-2</v>
+      </c>
+      <c r="AH43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI43" s="7">
+        <v>2</v>
+      </c>
+      <c r="AJ43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL43" s="7">
+        <v>2</v>
+      </c>
+      <c r="AM43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS43" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT43" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G44" s="7">
+        <v>23</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" s="7">
+        <v>1</v>
+      </c>
+      <c r="L44" s="7">
+        <v>1</v>
+      </c>
+      <c r="M44" s="7">
+        <v>1</v>
+      </c>
+      <c r="N44" s="7">
+        <v>2</v>
+      </c>
+      <c r="O44" s="7">
+        <v>2</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W44" s="7">
+        <v>1</v>
+      </c>
+      <c r="X44" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y44" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AB44" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="AC44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD44" s="7">
+        <v>1.54</v>
+      </c>
+      <c r="AE44" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AF44" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="7">
+        <v>-11</v>
+      </c>
+      <c r="AH44" s="7">
+        <v>16</v>
+      </c>
+      <c r="AI44" s="7">
+        <v>27</v>
+      </c>
+      <c r="AJ44" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AK44" s="7">
+        <v>11</v>
+      </c>
+      <c r="AL44" s="7">
+        <v>18</v>
+      </c>
+      <c r="AM44" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN44" s="7">
+        <v>13</v>
+      </c>
+      <c r="AO44" s="7">
+        <v>8</v>
+      </c>
+      <c r="AP44" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ44" s="7">
+        <v>3</v>
+      </c>
+      <c r="AR44" s="7">
+        <v>9</v>
+      </c>
+      <c r="AS44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT44" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="7">
+        <v>3</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G45" s="7">
+        <v>22</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I45" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="J45" s="7">
+        <v>1</v>
+      </c>
+      <c r="K45" s="7">
+        <v>1</v>
+      </c>
+      <c r="L45" s="7">
+        <v>2</v>
+      </c>
+      <c r="M45" s="7">
+        <v>2</v>
+      </c>
+      <c r="N45" s="7">
+        <v>3</v>
+      </c>
+      <c r="O45" s="7">
+        <v>3</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W45" s="7">
+        <v>2</v>
+      </c>
+      <c r="X45" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z45" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA45" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="AB45" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="AC45" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD45" s="7">
+        <v>1.62</v>
+      </c>
+      <c r="AE45" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="AF45" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="7">
+        <v>-6</v>
+      </c>
+      <c r="AH45" s="7">
+        <v>17</v>
+      </c>
+      <c r="AI45" s="7">
+        <v>23</v>
+      </c>
+      <c r="AJ45" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK45" s="7">
+        <v>12</v>
+      </c>
+      <c r="AL45" s="7">
+        <v>15</v>
+      </c>
+      <c r="AM45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN45" s="7">
+        <v>7</v>
+      </c>
+      <c r="AO45" s="7">
+        <v>4</v>
+      </c>
+      <c r="AP45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ45" s="7">
+        <v>2</v>
+      </c>
+      <c r="AR45" s="7">
+        <v>7</v>
+      </c>
+      <c r="AS45" s="7">
+        <v>1</v>
+      </c>
+      <c r="AT45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="7">
+        <v>3</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G46" s="7">
+        <v>24</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R46" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB46" s="7">
+        <v>-1.27</v>
+      </c>
+      <c r="AC46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD46" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="AE46" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="AF46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG46" s="7">
+        <v>-9</v>
+      </c>
+      <c r="AH46" s="7">
+        <v>6</v>
+      </c>
+      <c r="AI46" s="7">
+        <v>15</v>
+      </c>
+      <c r="AJ46" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK46" s="7">
+        <v>4</v>
+      </c>
+      <c r="AL46" s="7">
+        <v>9</v>
+      </c>
+      <c r="AM46" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AN46" s="7">
+        <v>4</v>
+      </c>
+      <c r="AO46" s="7">
+        <v>3</v>
+      </c>
+      <c r="AP46" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ46" s="7">
+        <v>2</v>
+      </c>
+      <c r="AR46" s="7">
+        <v>7</v>
+      </c>
+      <c r="AS46" s="7">
+        <v>1</v>
+      </c>
+      <c r="AT46" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="7">
+        <v>3</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G47" s="7">
+        <v>21</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N47" s="7">
+        <v>1</v>
+      </c>
+      <c r="O47" s="7">
+        <v>1</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X47" s="7">
+        <v>2</v>
+      </c>
+      <c r="Y47" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="AB47" s="7">
+        <v>-1.17</v>
+      </c>
+      <c r="AC47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD47" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="AE47" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="AF47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="7">
+        <v>-7</v>
+      </c>
+      <c r="AH47" s="7">
+        <v>7</v>
+      </c>
+      <c r="AI47" s="7">
+        <v>14</v>
+      </c>
+      <c r="AJ47" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK47" s="7">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="7">
+        <v>10</v>
+      </c>
+      <c r="AM47" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN47" s="7">
+        <v>2</v>
+      </c>
+      <c r="AO47" s="7">
+        <v>2</v>
+      </c>
+      <c r="AP47" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ47" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR47" s="7">
+        <v>4</v>
+      </c>
+      <c r="AS47" s="7">
+        <v>2</v>
+      </c>
+      <c r="AT47" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="7">
+        <v>3</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G48" s="7">
+        <v>16</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N48" s="7">
+        <v>-1</v>
+      </c>
+      <c r="O48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P48" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S48" s="7">
+        <v>7</v>
+      </c>
+      <c r="T48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U48" s="7">
+        <v>7</v>
+      </c>
+      <c r="V48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB48" s="7">
+        <v>-0.52</v>
+      </c>
+      <c r="AC48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD48" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="AE48" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="AF48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG48" s="7">
+        <v>-9</v>
+      </c>
+      <c r="AH48" s="7">
+        <v>2</v>
+      </c>
+      <c r="AI48" s="7">
+        <v>11</v>
+      </c>
+      <c r="AJ48" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK48" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL48" s="7">
+        <v>5</v>
+      </c>
+      <c r="AM48" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN48" s="7">
+        <v>5</v>
+      </c>
+      <c r="AO48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ48" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR48" s="7">
+        <v>2</v>
+      </c>
+      <c r="AS48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT48" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="7">
+        <v>3</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="7">
+        <v>19</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N49" s="7">
+        <v>-2</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P49" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>-0.53</v>
+      </c>
+      <c r="AC49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD49" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="AE49" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="AF49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG49" s="7">
+        <v>-10</v>
+      </c>
+      <c r="AH49" s="7">
+        <v>4</v>
+      </c>
+      <c r="AI49" s="7">
+        <v>14</v>
+      </c>
+      <c r="AJ49" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK49" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL49" s="7">
+        <v>11</v>
+      </c>
+      <c r="AM49" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN49" s="7">
+        <v>6</v>
+      </c>
+      <c r="AO49" s="7">
+        <v>5</v>
+      </c>
+      <c r="AP49" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="AQ49" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR49" s="7">
+        <v>5</v>
+      </c>
+      <c r="AS49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT49" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="7">
+        <v>3</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G50" s="7">
+        <v>21</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N50" s="7">
+        <v>-2</v>
+      </c>
+      <c r="O50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W50" s="7">
+        <v>2</v>
+      </c>
+      <c r="X50" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z50" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="AB50" s="7">
+        <v>-0.75</v>
+      </c>
+      <c r="AC50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD50" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="AE50" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="AF50" s="7">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="7">
+        <v>-13</v>
+      </c>
+      <c r="AH50" s="7">
+        <v>4</v>
+      </c>
+      <c r="AI50" s="7">
+        <v>17</v>
+      </c>
+      <c r="AJ50" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK50" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL50" s="7">
+        <v>11</v>
+      </c>
+      <c r="AM50" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN50" s="7">
+        <v>12</v>
+      </c>
+      <c r="AO50" s="7">
+        <v>6</v>
+      </c>
+      <c r="AP50" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ50" s="7">
+        <v>1</v>
+      </c>
+      <c r="AR50" s="7">
+        <v>9</v>
+      </c>
+      <c r="AS50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT50" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:46" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="7">
+        <v>3</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="G51" s="7">
+        <v>4</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="X51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE51" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="AF51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG51" s="7">
+        <v>-3</v>
+      </c>
+      <c r="AH51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI51" s="7">
+        <v>3</v>
+      </c>
+      <c r="AJ51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL51" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN51" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO51" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP51" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR51" s="7">
+        <v>1</v>
+      </c>
+      <c r="AS51" s="7">
+        <v>1</v>
+      </c>
+      <c r="AT51" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5794,7 +8237,7 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E1:AT1 A1:B1 A34" numberStoredAsText="1"/>
+    <ignoredError sqref="E1:AT1 A1:B1 A34 A42" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>